--- a/artfynd/A 34232-2024 artfynd.xlsx
+++ b/artfynd/A 34232-2024 artfynd.xlsx
@@ -3505,11 +3505,11 @@
         <v>120655229</v>
       </c>
       <c r="B26" t="n">
-        <v>91119</v>
+        <v>91168</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">

--- a/artfynd/A 34232-2024 artfynd.xlsx
+++ b/artfynd/A 34232-2024 artfynd.xlsx
@@ -3505,7 +3505,7 @@
         <v>120655229</v>
       </c>
       <c r="B26" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 34232-2024 artfynd.xlsx
+++ b/artfynd/A 34232-2024 artfynd.xlsx
@@ -3505,7 +3505,7 @@
         <v>120655229</v>
       </c>
       <c r="B26" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 34232-2024 artfynd.xlsx
+++ b/artfynd/A 34232-2024 artfynd.xlsx
@@ -3505,7 +3505,7 @@
         <v>120655229</v>
       </c>
       <c r="B26" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 34232-2024 artfynd.xlsx
+++ b/artfynd/A 34232-2024 artfynd.xlsx
@@ -3505,7 +3505,7 @@
         <v>120655229</v>
       </c>
       <c r="B26" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 34232-2024 artfynd.xlsx
+++ b/artfynd/A 34232-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120636795</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>120636772</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>120636711</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>120636390</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>120636405</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>120636483</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>120665197</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>120656907</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>120664724</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>120656859</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>120656748</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>120656878</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>120668226</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
